--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28 18:56:14</t>
+          <t>2026-07-28 14:39:50</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29 09:56:14</t>
+          <t>2026-07-29 05:39:50</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28 14:39:50</t>
+          <t>2026-07-28 14:42:03</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29 05:39:50</t>
+          <t>2026-07-29 05:42:03</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28 14:42:03</t>
+          <t>2026-07-29 06:14:16</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29 05:42:03</t>
+          <t>2026-07-29 21:14:16</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29 06:14:16</t>
+          <t>2026-07-29 11:39:39</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29 21:14:16</t>
+          <t>2026-07-30 02:39:39</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29 11:39:39</t>
+          <t>2026-07-30 06:05:42</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30 02:39:39</t>
+          <t>2026-07-30 21:05:42</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30 06:05:42</t>
+          <t>2026-07-30 11:28:33</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30 21:05:42</t>
+          <t>2026-07-31 02:28:33</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30 11:28:33</t>
+          <t>2026-07-30 14:01:25</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31 02:28:33</t>
+          <t>2026-07-31 05:01:25</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-30 14:01:25</t>
+          <t>2026-07-31 06:29:13</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31 05:01:25</t>
+          <t>2026-07-31 21:29:13</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31 06:29:13</t>
+          <t>2026-07-31 11:38:34</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31 21:29:13</t>
+          <t>2026-08-01 02:38:35</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31 11:38:34</t>
+          <t>2026-08-01 06:14:28</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 02:38:35</t>
+          <t>2026-08-01 21:14:28</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 06:14:28</t>
+          <t>2026-08-01 10:57:53</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 21:14:28</t>
+          <t>2026-08-02 01:57:53</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01 10:57:53</t>
+          <t>2026-08-02 06:17:47</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02 01:57:53</t>
+          <t>2026-08-02 21:17:47</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02 06:17:47</t>
+          <t>2026-08-02 10:57:55</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02 21:17:47</t>
+          <t>2026-08-03 01:57:55</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02 10:57:55</t>
+          <t>2026-08-03 06:53:37</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03 01:57:55</t>
+          <t>2026-08-03 21:53:37</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03 06:53:37</t>
+          <t>2026-08-03 12:42:29</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03 21:53:37</t>
+          <t>2026-08-04 03:42:29</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-03 12:42:29</t>
+          <t>2026-08-04 06:10:06</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 03:42:29</t>
+          <t>2026-08-04 21:10:06</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 06:10:06</t>
+          <t>2026-08-04 11:38:29</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 21:10:06</t>
+          <t>2026-08-05 02:38:29</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04 11:38:29</t>
+          <t>2026-08-05 06:06:11</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 02:38:29</t>
+          <t>2026-08-05 21:06:11</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 06:06:11</t>
+          <t>2026-08-05 11:36:46</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 21:06:11</t>
+          <t>2026-08-06 02:36:46</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-05 11:36:46</t>
+          <t>2026-08-06 06:10:26</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 02:36:46</t>
+          <t>2026-08-06 21:10:26</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 06:10:26</t>
+          <t>2026-08-06 11:40:18</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 21:10:26</t>
+          <t>2026-08-07 02:40:18</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-06 11:40:18</t>
+          <t>2026-08-07 05:12:17</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07 02:40:18</t>
+          <t>2026-08-07 20:12:17</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07 05:12:17</t>
+          <t>2026-08-07 10:25:03</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07 20:12:17</t>
+          <t>2026-08-08 01:25:03</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07 10:25:03</t>
+          <t>2026-08-08 04:34:58</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08 01:25:03</t>
+          <t>2026-08-08 19:34:58</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08 04:34:58</t>
+          <t>2026-08-08 10:02:56</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08 19:34:58</t>
+          <t>2026-08-09 01:02:56</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08 10:02:56</t>
+          <t>2026-08-09 04:45:44</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09 01:02:56</t>
+          <t>2026-08-09 19:45:44</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09 04:45:44</t>
+          <t>2026-08-09 10:04:51</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09 19:45:44</t>
+          <t>2026-08-10 01:04:51</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09 10:04:51</t>
+          <t>2026-08-10 05:05:21</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10 01:04:51</t>
+          <t>2026-08-10 20:05:21</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10 05:05:21</t>
+          <t>2026-08-10 10:42:47</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10 20:05:21</t>
+          <t>2026-08-11 01:42:47</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10 10:42:47</t>
+          <t>2026-08-11 04:48:01</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 01:42:47</t>
+          <t>2026-08-11 19:48:01</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 04:48:01</t>
+          <t>2026-08-11 10:24:37</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 19:48:01</t>
+          <t>2026-08-12 01:24:37</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11 10:24:37</t>
+          <t>2026-08-12 05:13:15</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12 01:24:37</t>
+          <t>2026-08-12 20:13:15</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12 05:13:15</t>
+          <t>2026-08-12 10:34:20</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12 20:13:15</t>
+          <t>2026-08-13 01:34:20</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12 10:34:20</t>
+          <t>2026-08-13 05:17:30</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13 01:34:20</t>
+          <t>2026-08-13 20:17:30</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13 05:17:30</t>
+          <t>2026-08-13 10:35:14</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13 20:17:30</t>
+          <t>2026-08-14 01:35:14</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-13 10:35:14</t>
+          <t>2026-08-14 05:14:16</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14 01:35:14</t>
+          <t>2026-08-14 20:14:16</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14 05:14:16</t>
+          <t>2026-08-14 10:32:29</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14 20:14:16</t>
+          <t>2026-08-15 01:32:29</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14 10:32:29</t>
+          <t>2026-08-15 04:03:24</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15 01:32:29</t>
+          <t>2026-08-15 19:03:24</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15 04:03:24</t>
+          <t>2026-08-15 09:49:11</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15 19:03:24</t>
+          <t>2026-08-16 00:49:11</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15 09:49:11</t>
+          <t>2026-08-16 04:07:54</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16 00:49:11</t>
+          <t>2026-08-16 19:07:54</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16 04:07:54</t>
+          <t>2026-08-16 09:50:29</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16 19:07:54</t>
+          <t>2026-08-17 00:50:29</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16 09:50:29</t>
+          <t>2026-08-17 04:11:08</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17 00:50:29</t>
+          <t>2026-08-17 19:11:08</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17 04:11:08</t>
+          <t>2026-08-17 10:04:20</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17 19:11:08</t>
+          <t>2026-08-18 01:04:20</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17 10:04:20</t>
+          <t>2026-08-18 04:06:13</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18 01:04:20</t>
+          <t>2026-08-18 19:06:13</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18 04:06:13</t>
+          <t>2026-08-18 09:57:18</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18 19:06:13</t>
+          <t>2026-08-19 00:57:18</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-18 09:57:18</t>
+          <t>2026-08-19 04:06:52</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19 00:57:18</t>
+          <t>2026-08-19 19:06:52</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19 04:06:52</t>
+          <t>2026-08-19 09:58:00</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19 19:06:52</t>
+          <t>2026-08-20 00:58:00</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19 09:58:00</t>
+          <t>2026-08-20 04:06:49</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20 00:58:00</t>
+          <t>2026-08-20 19:06:49</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20 04:06:49</t>
+          <t>2026-08-20 10:00:05</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20 19:06:49</t>
+          <t>2026-08-21 01:00:05</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20 10:00:05</t>
+          <t>2026-08-21 04:08:57</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 01:00:05</t>
+          <t>2026-08-21 19:08:57</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 04:08:57</t>
+          <t>2026-08-21 09:59:46</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 19:08:57</t>
+          <t>2026-08-22 00:59:46</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21 09:59:46</t>
+          <t>2026-08-22 04:04:35</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 00:59:46</t>
+          <t>2026-08-22 19:04:35</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 04:04:35</t>
+          <t>2026-08-22 09:50:20</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 19:04:35</t>
+          <t>2026-08-23 00:50:20</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22 09:50:20</t>
+          <t>2026-08-23 04:08:20</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23 00:50:20</t>
+          <t>2026-08-23 19:08:20</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23 04:08:20</t>
+          <t>2026-08-23 09:52:17</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23 19:08:20</t>
+          <t>2026-08-24 00:52:17</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23 09:52:17</t>
+          <t>2026-08-24 04:13:30</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24 00:52:17</t>
+          <t>2026-08-24 19:13:30</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24 04:13:30</t>
+          <t>2026-08-24 10:10:02</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24 19:13:30</t>
+          <t>2026-08-25 01:10:02</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24 10:10:02</t>
+          <t>2026-08-25 04:08:19</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25 01:10:02</t>
+          <t>2026-08-25 19:08:19</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25 04:08:19</t>
+          <t>2026-08-25 10:00:14</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25 19:08:19</t>
+          <t>2026-08-26 01:00:14</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-25 10:00:14</t>
+          <t>2026-08-26 04:10:03</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26 01:00:14</t>
+          <t>2026-08-26 19:10:03</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26 04:10:03</t>
+          <t>2026-08-26 10:05:12</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26 19:10:03</t>
+          <t>2026-08-27 01:05:12</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-26 10:05:12</t>
+          <t>2026-08-27 11:47:05</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27 01:05:12</t>
+          <t>2026-08-28 02:47:05</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27 11:47:05</t>
+          <t>2026-08-27 14:25:30</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28 02:47:05</t>
+          <t>2026-08-28 05:25:30</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-27 14:25:30</t>
+          <t>2026-08-28 15:33:36</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28 05:25:30</t>
+          <t>2026-08-29 06:33:36</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-28 15:33:36</t>
+          <t>2026-08-29 10:18:28</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29 06:33:36</t>
+          <t>2026-08-30 01:18:28</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29 10:18:28</t>
+          <t>2026-08-30 09:23:45</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30 01:18:28</t>
+          <t>2026-08-31 00:23:45</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30 09:23:45</t>
+          <t>2026-08-30 14:29:06</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31 00:23:45</t>
+          <t>2026-08-31 05:29:06</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30 14:29:06</t>
+          <t>2026-08-31 09:58:34</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31 05:29:06</t>
+          <t>2026-09-01 00:58:34</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31 09:58:34</t>
+          <t>2026-09-01 08:50:03</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01 00:58:34</t>
+          <t>2026-09-01 23:50:03</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01 08:50:03</t>
+          <t>2026-09-01 14:14:36</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01 23:50:03</t>
+          <t>2026-09-02 05:14:36</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01 14:14:36</t>
+          <t>2026-09-02 08:02:55</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 05:14:36</t>
+          <t>2026-09-02 23:02:55</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 08:02:55</t>
+          <t>2026-09-02 13:46:37</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 23:02:55</t>
+          <t>2026-09-03 04:46:37</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-02 13:46:37</t>
+          <t>2026-09-03 08:12:43</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03 04:46:37</t>
+          <t>2026-09-03 23:12:43</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03 08:12:43</t>
+          <t>2026-09-03 13:44:34</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03 23:12:43</t>
+          <t>2026-09-04 04:44:34</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-03 13:44:34</t>
+          <t>2026-09-04 08:08:02</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04 04:44:34</t>
+          <t>2026-09-04 23:08:02</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04 08:08:02</t>
+          <t>2026-09-04 13:40:33</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04 23:08:02</t>
+          <t>2026-09-05 04:40:33</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04 13:40:33</t>
+          <t>2026-09-05 07:48:05</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05 04:40:33</t>
+          <t>2026-09-05 22:48:05</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05 07:48:05</t>
+          <t>2026-09-05 12:54:36</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05 22:48:05</t>
+          <t>2026-09-06 03:54:36</t>
         </is>
       </c>
     </row>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05 12:54:36</t>
+          <t>2026-09-06 08:02:02</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06 03:54:36</t>
+          <t>2026-09-06 23:02:02</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06 08:02:02</t>
+          <t>2026-09-06 13:01:40</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06 23:02:02</t>
+          <t>2026-09-07 04:01:40</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-06 13:01:40</t>
+          <t>2026-09-07 08:32:29</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07 04:01:40</t>
+          <t>2026-09-07 23:32:29</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07 08:32:29</t>
+          <t>2026-09-07 15:08:56</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07 23:32:29</t>
+          <t>2026-09-08 06:08:56</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07 15:08:56</t>
+          <t>2026-09-08 08:15:11</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08 06:08:56</t>
+          <t>2026-09-08 23:15:11</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08 08:15:11</t>
+          <t>2026-09-08 13:46:06</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08 23:15:11</t>
+          <t>2026-09-09 04:46:06</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08 13:46:06</t>
+          <t>2026-09-09 08:18:27</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09 04:46:06</t>
+          <t>2026-09-09 23:18:27</t>
         </is>
       </c>
     </row>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09 08:18:27</t>
+          <t>2026-09-09 13:49:25</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09 23:18:27</t>
+          <t>2026-09-10 04:49:25</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09 13:49:25</t>
+          <t>2026-09-10 08:17:58</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10 04:49:25</t>
+          <t>2026-09-10 23:17:58</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10 08:17:58</t>
+          <t>2026-09-10 13:45:54</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10 23:17:58</t>
+          <t>2026-09-11 04:45:54</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10 13:45:54</t>
+          <t>2026-09-11 08:12:56</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11 04:45:54</t>
+          <t>2026-09-11 23:12:56</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11 08:12:56</t>
+          <t>2026-09-11 13:42:39</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11 23:12:56</t>
+          <t>2026-09-12 04:42:39</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11 13:42:39</t>
+          <t>2026-09-12 08:03:00</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12 04:42:39</t>
+          <t>2026-09-12 23:03:00</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12 08:03:00</t>
+          <t>2026-09-12 12:59:07</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12 23:03:00</t>
+          <t>2026-09-13 03:59:07</t>
         </is>
       </c>
     </row>
@@ -395,7 +395,7 @@
       </c>
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>

--- a/files/main.xlsx
+++ b/files/main.xlsx
@@ -378,12 +378,12 @@
       <c r="C12" s="6" t="n"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-12 12:59:07</t>
+          <t>2026-09-13 08:28:16</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-13 03:59:07</t>
+          <t>2026-09-13 23:28:16</t>
         </is>
       </c>
     </row>
@@ -408,7 +408,7 @@
       </c>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
@@ -422,7 +422,7 @@
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D15" s="4" t="n"/>
